--- a/stories/arbres/TREE-EMO-008.xlsx
+++ b/stories/arbres/TREE-EMO-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le train, Sami tient une gourde. Un peu d'eau tombe sur le manteau de Léa. Les joues de Sami deviennent chaudes. Papa est à côté. Maman arrivera à la gare. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1511,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a reçu une goutte. Sami est gêné. C'est Tom. Le seau sonne, tout léger. Sami s'approche, sans courir. Maman n'est pas loin. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a les joues chaudes après une erreur. Que fait-on ? Avec Tom.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Sami retient le geste. Il respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2229,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes, après Tom. Un ruisseau chante tout bas. Sami montre les cubes à papa. Il nomme ce qu'il sent. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2587,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2559,7 +2616,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint une pomme, après Tom et les cubes. La tasse est encore tiède. On dit merci. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. Le soleil est encore là.</t>
+          <t>Sami rejoint une pomme, après Tom et les cubes. La tasse est encore tiède. On dit merci. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2697,6 +2754,13 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Tom et les cubes. La tasse est encore tiède. On dit merci. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2923,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2883,7 +2952,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un yaourt, après Tom et les cubes. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On gardu geste.</t>
+          <t>Sami rejoint un yaourt, après Tom et les cubes. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3021,6 +3090,12 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Tom et les cubes. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3258,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3207,7 +3287,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un morceau de pain, après Tom et les cubes. Une abeille bourdonne loin. On attend un petit moment. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+          <t>Sami rejoint un morceau de pain, après Tom et les cubes. Une abeille bourdonne loin. On attend un petit moment. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3345,6 +3425,12 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Tom et les cubes. Une abeille bourdonne loin. On attend un petit moment. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre, après Tom. Une goutte de pluie sèche déjà. Le livre est là. Sami pose les mains à vue, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3951,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3980,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint une pomme, après Tom et le livre. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On respire.</t>
+          <t>Sami rejoint une pomme, après Tom et le livre. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4118,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Tom et le livre. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4203,7 +4315,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un yaourt, après Tom et le livre. La fenêtre tremble un tout petit peu. On sourit un peu. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
+          <t>Sami rejoint un yaourt, après Tom et le livre. La fenêtre tremble un tout petit peu. On sourit un peu. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4341,6 +4453,12 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Tom et le livre. La fenêtre tremble un tout petit peu. On sourit un peu. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4621,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4650,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un morceau de pain, après Tom et le livre. Ça sent le savon de maman. On boit une gorgée d'eau. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. Le jeu peut recommencer.</t>
+          <t>Sami rejoint un morceau de pain, après Tom et le livre. Ça sent le savon de maman. On boit une gorgée d'eau. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4788,13 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Tom et le livre. Ça sent le savon de maman. On boit une gorgée d'eau. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4957,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5124,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette, après Tom. Un pigeon roucoule. La dînette est là. Sami pose les mains à vue, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5315,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5199,7 +5344,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint une pomme, après Tom et la dînette. Un pigeon roucoule. On essuie une miette. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On se serre un peu.</t>
+          <t>Sami rejoint une pomme, après Tom et la dînette. Un pigeon roucoule. On essuie une miette. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5337,6 +5482,12 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Tom et la dînette. Un pigeon roucoule. On essuie une miette. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5650,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5523,7 +5679,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un yaourt, après Tom et la dînette. La cuillère tinte. On referme un livre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On rentre.</t>
+          <t>Sami rejoint un yaourt, après Tom et la dînette. La cuillère tinte. On referme un livre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5661,6 +5817,12 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Tom et la dînette. La cuillère tinte. On referme un livre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5985,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5847,7 +6014,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un morceau de pain, après Tom et la dînette. Le ballon est un peu poudreux. On pose un jouet à sa place. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. La journée continue, tout doux.</t>
+          <t>Sami rejoint un morceau de pain, après Tom et la dînette. Le ballon est un peu poudreux. On pose un jouet à sa place. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5985,6 +6152,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Tom et la dînette. Le ballon est un peu poudreux. On pose un jouet à sa place. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6321,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6309,6 +6488,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa essuie sa manche. Sami est gêné. Sami s'occupe de Léa. Une goutte tombe dans l'évier. Papa sourit. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6673,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a les joues chaudes après une erreur. Que fait-on ? Avec Léa.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6846,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Sami répète le mot. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7037,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7204,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes, après Léa. Une goutte tombe dans l'évier. On parle des cubes. Sami écoute jusqu'au bout. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7395,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7215,7 +7424,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint une pomme, après Léa et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
+          <t>Sami rejoint une pomme, après Léa et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7353,6 +7562,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Léa et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7730,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7539,7 +7759,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un yaourt, après Léa et les cubes. Le banc est tiède. On se tait une seconde. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. Le soleil est encore là.</t>
+          <t>Sami rejoint un yaourt, après Léa et les cubes. Le banc est tiède. On se tait une seconde. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7677,6 +7897,13 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Léa et les cubes. Le banc est tiède. On se tait une seconde. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8066,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7863,7 +8095,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un morceau de pain, après Léa et les cubes. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On gardu geste.</t>
+          <t>Sami rejoint un morceau de pain, après Léa et les cubes. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8001,6 +8233,12 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Léa et les cubes. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8401,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8568,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre, après Léa. Il y a des miettes sur la table. Près du livre, Sami prend le temps. Pas de course. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8759,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8535,7 +8788,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint une pomme, après Léa et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+          <t>Sami rejoint une pomme, après Léa et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8673,6 +8926,12 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Léa et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9094,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8859,7 +9123,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un yaourt, après Léa et le livre. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On respire.</t>
+          <t>Sami rejoint un yaourt, après Léa et le livre. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -8997,6 +9261,12 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Léa et le livre. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9183,7 +9458,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un morceau de pain, après Léa et le livre. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
+          <t>Sami rejoint un morceau de pain, après Léa et le livre. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9321,6 +9596,12 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Léa et le livre. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9764,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9931,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette, après Léa. La pomme est croquante. On continue avec la dînette. Sami gardu geste sûr. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10122,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9855,7 +10151,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint une pomme, après Léa et la dînette. Une plume vole. On range les chaussures. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. Le jeu peut recommencer.</t>
+          <t>Sami rejoint une pomme, après Léa et la dînette. Une plume vole. On range les chaussures. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9993,6 +10289,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Léa et la dînette. Une plume vole. On range les chaussures. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10458,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10179,7 +10487,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un yaourt, après Léa et la dînette. Le pain croustille. On met le doudou près de soi. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On se serre un peu.</t>
+          <t>Sami rejoint un yaourt, après Léa et la dînette. Le pain croustille. On met le doudou près de soi. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10317,6 +10625,12 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Léa et la dînette. Le pain croustille. On met le doudou près de soi. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10503,7 +10822,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint un morceau de pain, après Léa et la dînette. La laine du doudou est douce. On écoute le cœur, tout doux. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Papa dit : je t'ai entendu. Maman aussi. On rentre.</t>
+          <t>Sami rejoint un morceau de pain, après Léa et la dînette. La laine du doudou est douce. On écoute le cœur, tout doux. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10641,6 +10960,12 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Léa et la dînette. La laine du doudou est douce. On écoute le cœur, tout doux. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.
+papa|Je t'ai entendu. Maman aussi. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11128,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10965,6 +11295,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami voit sa propre gourde. Il est gêné de l'erreur. Voilà Sami. Le train souffle au loin. Sami pose les pieds par terre, près de papa. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11145,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a les joues chaudes après une erreur. Que fait-on ? Avec Sami.</t>
         </is>
       </c>
     </row>
@@ -11313,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Sami pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11499,6 +11844,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11523,7 +11873,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi les cubes, après Sami. La fenêtre tremble un tout petit peu. Sami touche les cubes tout doucement. Papa dit : je suis là. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+          <t>Sami a choisi les cubes, après Sami. La fenêtre tremble un tout petit peu. Sami touche les cubes tout doucement. Je suis là. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11661,6 +12011,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes, après Sami. La fenêtre tremble un tout petit peu. Sami touche les cubes tout doucement.
+papa|Je suis là.
+narrateur|Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11847,6 +12204,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12009,6 +12371,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Sami et les cubes. Un galet est lisse dans la main. On secoue les mains, loin. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse une pomme à sa place. Sami est près de papa. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12538,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12705,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Sami et les cubes. Le train souffle au loin. On pose le sac. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un yaourt à sa place. Sami est près de papa. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12872,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13039,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Sami et les cubes. Une vache meugle, loin. On dit le mot de l'émotion. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un morceau de pain à sa place. Sami est près de papa. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13206,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13373,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre, après Sami. Une plume vole. Près du livre, Sami prend le temps. Pas de course. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13167,6 +13564,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13329,6 +13731,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Sami et le livre. Un grillon chante, tout petit. On invite d'une petite voix. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse une pomme à sa place. Sami est près de papa. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13491,6 +13898,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13653,6 +14065,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Sami et le livre. Le bois de la table est lisse. On attend la réponse. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un yaourt à sa place. Sami est près de papa. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13815,6 +14232,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13977,6 +14399,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Sami et le livre. Une goutte tombe dans l'évier. On propose une autre idée. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un morceau de pain à sa place. Sami est près de papa. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14139,6 +14566,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14301,6 +14733,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette, après Sami. Un ruisseau chante tout bas. La dînette est là. Sami pose les mains à vue, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14487,6 +14924,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14649,6 +15091,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint une pomme, après Sami et la dînette. Le toboggan est un peu froid. On va vers papa ou maman. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse une pomme à sa place. Sami est près de papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14811,6 +15258,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14973,6 +15425,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un yaourt, après Sami et la dînette. La clochette de la porte tinte. On dit stop, tout clair. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un yaourt à sa place. Sami est près de papa. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15135,6 +15592,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15297,6 +15759,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint un morceau de pain, après Sami et la dînette. Ça sent le thym du jardin. On s'éloigne d'un pas. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un morceau de pain à sa place. Sami est près de papa. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15459,6 +15926,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15477,7 +15949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15494,6 +15966,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-008.xlsx
+++ b/stories/arbres/TREE-EMO-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Dans le train, Sami tient une gourde. Un peu d'eau tombe sur le manteau de Léa. Les joues de Sami deviennent chaudes. Papa est à côté. Maman arrivera à la gare. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Tom a reçu une goutte. Sami est gêné. C'est Tom. Le seau sonne, tout léger. Sami s'approche, sans courir. Maman n'est pas loin. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|Sami a les joues chaudes après une erreur. Que fait-on ? Avec Tom.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Oui. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Sami retient le geste. Il respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2244,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2412,7 @@
           <t>narrateur|Sami a choisi les cubes, après Tom. Un ruisseau chante tout bas. Sami montre les cubes à papa. Il nomme ce qu'il sent. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2604,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2761,6 +2774,7 @@
 narrateur|Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2928,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3096,6 +3111,7 @@
 papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3263,6 +3279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3448,7 @@
 papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3784,7 @@
           <t>narrateur|Sami a choisi le livre, après Tom. Une goutte de pluie sèche déjà. Le livre est là. Sami pose les mains à vue, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3956,6 +3976,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
 papa|Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4459,6 +4482,7 @@
 papa|Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4626,6 +4650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4795,6 +4820,7 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4962,6 +4988,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5129,6 +5156,7 @@
           <t>narrateur|Sami a choisi la dînette, après Tom. Un pigeon roucoule. La dînette est là. Sami pose les mains à vue, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5320,6 +5348,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
 papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5823,6 +5854,7 @@
 papa|Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5990,6 +6022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6159,6 +6192,7 @@
 narrateur|La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6326,6 +6360,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6493,6 +6528,7 @@
           <t>narrateur|Léa essuie sa manche. Sami est gêné. Sami s'occupe de Léa. Une goutte tombe dans l'évier. Papa sourit. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6680,6 +6716,7 @@
           <t>narrateur|Sami a les joues chaudes après une erreur. Que fait-on ? Avec Léa.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6851,6 +6888,7 @@
           <t>narrateur|Oui. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Sami répète le mot. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7042,6 +7080,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7209,6 +7248,7 @@
           <t>narrateur|Sami a choisi les cubes, après Léa. Une goutte tombe dans l'évier. On parle des cubes. Sami écoute jusqu'au bout. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7400,6 +7440,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7568,6 +7609,7 @@
 papa|Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7735,6 +7777,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7904,6 +7947,7 @@
 narrateur|Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8071,6 +8115,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8239,6 +8284,7 @@
 papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8406,6 +8452,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8573,6 +8620,7 @@
           <t>narrateur|Sami a choisi le livre, après Léa. Il y a des miettes sur la table. Près du livre, Sami prend le temps. Pas de course. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8764,6 +8812,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8932,6 +8981,7 @@
 papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9099,6 +9149,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
 papa|Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9602,6 +9655,7 @@
 papa|Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9769,6 +9823,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9936,6 +9991,7 @@
           <t>narrateur|Sami a choisi la dînette, après Léa. La pomme est croquante. On continue avec la dînette. Sami gardu geste sûr. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10127,6 +10183,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10296,6 +10353,7 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10463,6 +10521,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
 papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10966,6 +11027,7 @@
 papa|Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11133,6 +11195,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
           <t>narrateur|Sami voit sa propre gourde. Il est gêné de l'erreur. Voilà Sami. Le train souffle au loin. Sami pose les pieds par terre, près de papa. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Sami a les joues chaudes après une erreur. Que fait-on ? Avec Sami.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. Sami pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12018,6 +12085,7 @@
 narrateur|Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12209,6 +12277,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12376,6 +12445,7 @@
           <t>narrateur|Sami rejoint une pomme, après Sami et les cubes. Un galet est lisse dans la main. On secoue les mains, loin. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse une pomme à sa place. Sami est près de papa. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12543,6 +12613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12710,6 +12781,7 @@
           <t>narrateur|Sami rejoint un yaourt, après Sami et les cubes. Le train souffle au loin. On pose le sac. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un yaourt à sa place. Sami est près de papa. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12877,6 +12949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13044,6 +13117,7 @@
           <t>narrateur|Sami rejoint un morceau de pain, après Sami et les cubes. Une vache meugle, loin. On dit le mot de l'émotion. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un morceau de pain à sa place. Sami est près de papa. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13211,6 +13285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13378,6 +13453,7 @@
           <t>narrateur|Sami a choisi le livre, après Sami. Une plume vole. Près du livre, Sami prend le temps. Pas de course. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13569,6 +13645,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13736,6 +13813,7 @@
           <t>narrateur|Sami rejoint une pomme, après Sami et le livre. Un grillon chante, tout petit. On invite d'une petite voix. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse une pomme à sa place. Sami est près de papa. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13903,6 +13981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14070,6 +14149,7 @@
           <t>narrateur|Sami rejoint un yaourt, après Sami et le livre. Le bois de la table est lisse. On attend la réponse. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un yaourt à sa place. Sami est près de papa. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14237,6 +14317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14404,6 +14485,7 @@
           <t>narrateur|Sami rejoint un morceau de pain, après Sami et le livre. Une goutte tombe dans l'évier. On propose une autre idée. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un morceau de pain à sa place. Sami est près de papa. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14571,6 +14653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14738,6 +14821,7 @@
           <t>narrateur|Sami a choisi la dînette, après Sami. Un ruisseau chante tout bas. La dînette est là. Sami pose les mains à vue, loin de l'autre. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14929,6 +15013,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15096,6 +15181,7 @@
           <t>narrateur|Sami rejoint une pomme, après Sami et la dînette. Le toboggan est un peu froid. On va vers papa ou maman. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse une pomme à sa place. Sami est près de papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15263,6 +15349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15430,6 +15517,7 @@
           <t>narrateur|Sami rejoint un yaourt, après Sami et la dînette. La clochette de la porte tinte. On dit stop, tout clair. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un yaourt à sa place. Sami est près de papa. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15597,6 +15685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15764,6 +15853,7 @@
           <t>narrateur|Sami rejoint un morceau de pain, après Sami et la dînette. Ça sent le thym du jardin. On s'éloigne d'un pas. Sami se sent gêné. Les joues sont chaudes. Une erreur ne dit pas qui on est. Sami dit l'erreur. Il répare, avec papa. On laisse un morceau de pain à sa place. Sami est près de papa. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15931,6 +16021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15949,7 +16040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15973,6 +16064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15987,7 +16092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16174,6 +16279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
